--- a/ConfigExporter/xlsx/ui_page.xlsx
+++ b/ConfigExporter/xlsx/ui_page.xlsx
@@ -1,175 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB807448-B27B-4F70-9721-F1A53FBE9C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8115" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8115" yWindow="5535" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ui_page" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ui_page" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#require#unique</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#remarks</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LoadingPage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所在context层级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>contextType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Loading</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#require#enum(General,Header,Loading,TopMost)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isLoadAsync</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否异步加载</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>boolean</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#require</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SavingPopup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainMenuPage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>General</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景加载界面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主菜单界面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否为弹窗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>isPopup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用户信息弹窗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UserInfoPopup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存档中右下提示弹窗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对弈主界面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DuelPage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Header</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DuelSetupPopup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对弈设置弹窗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -209,37 +74,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -505,93 +429,143 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="17.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="17.25" style="1" customWidth="1"/>
+    <col width="17.625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="17.25" customWidth="1" style="1" min="2" max="2"/>
+    <col width="23.625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="17.25" customWidth="1" style="1" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>9</v>
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>所在context层级</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>是否为弹窗</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>是否异步加载</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>#remarks</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>contextType</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>isPopup</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>isLoadAsync</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28.5" customFormat="1" customHeight="1" s="6">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>#require#unique</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>#require#enum(General,Header,Loading,TopMost)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>LoadingPage</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>场景加载界面</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
       </c>
       <c r="D5" s="4" t="b">
         <v>0</v>
@@ -600,15 +574,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MainMenuPage</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>主菜单界面</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
       </c>
       <c r="D6" s="4" t="b">
         <v>0</v>
@@ -617,15 +597,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>9</v>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SavingPopup</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>存档中右下提示弹窗</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
@@ -634,15 +620,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>UserInfoPopup</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>用户信息弹窗</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
       </c>
       <c r="D8" s="4" t="b">
         <v>1</v>
@@ -651,15 +643,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>17</v>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>DuelSetupPopup</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>对弈设置弹窗</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
       </c>
       <c r="D9" s="4" t="b">
         <v>1</v>
@@ -668,15 +666,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>27</v>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DuelPage</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>对弈主界面</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
       </c>
       <c r="D10" s="4" t="b">
         <v>0</v>
@@ -685,8 +689,30 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ConfirmPopup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>generic confirm popup</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TopMost</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ConfigExporter/xlsx/ui_page.xlsx
+++ b/ConfigExporter/xlsx/ui_page.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.625" customWidth="1" style="1" min="1" max="1"/>
@@ -644,46 +644,46 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>DuelSetupPopup</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>对弈设置弹窗</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="b">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ReplayPage</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>复盘界面</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>DuelPage</t>
+          <t>DuelSetupPopup</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>对弈主界面</t>
+          <t>对弈设置弹窗</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D10" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="4" t="b">
         <v>1</v>
@@ -692,23 +692,69 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>LanRoomPopup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>局域网房间弹窗</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>DuelPage</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>对弈主界面</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>ConfirmPopup</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>generic confirm popup</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>TopMost</t>
         </is>
       </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="b">
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
         <v>0</v>
       </c>
     </row>

--- a/ConfigExporter/xlsx/ui_page.xlsx
+++ b/ConfigExporter/xlsx/ui_page.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.625" customWidth="1" style="1" min="1" max="1"/>
@@ -600,161 +600,138 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>SavingPopup</t>
+          <t>UserInfoPopup</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>存档中右下提示弹窗</t>
+          <t>用户信息弹窗</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Loading</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ReplayPage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>复盘界面</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>UserInfoPopup</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>用户信息弹窗</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>DuelSetupPopup</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>对弈设置弹窗</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ReplayPage</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>复盘界面</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LanRoomPopup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>局域网房间弹窗</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DuelPage</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>对弈主界面</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="D9" t="b">
+      <c r="D11" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>DuelSetupPopup</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>对弈设置弹窗</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LanRoomPopup</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>局域网房间弹窗</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="b">
+      <c r="E11" s="4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>DuelPage</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>对弈主界面</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>ConfirmPopup</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>generic confirm popup</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>TopMost</t>
         </is>
       </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="b">
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
         <v>0</v>
       </c>
     </row>

--- a/ConfigExporter/xlsx/ui_page.xlsx
+++ b/ConfigExporter/xlsx/ui_page.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.625" customWidth="1" style="1" min="1" max="1"/>
@@ -469,6 +469,11 @@
           <t>是否异步加载</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>场景退出时关闭</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -496,6 +501,11 @@
           <t>isLoadAsync</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>closeOnSceneExit</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -523,6 +533,11 @@
           <t>boolean</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28.5" customFormat="1" customHeight="1" s="6">
       <c r="A4" s="5" t="inlineStr">
@@ -550,6 +565,11 @@
           <t>#require</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -573,6 +593,9 @@
       <c r="E5" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -596,6 +619,9 @@
       <c r="E6" s="4" t="b">
         <v>1</v>
       </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -619,6 +645,9 @@
       <c r="E7" s="4" t="b">
         <v>1</v>
       </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -642,6 +671,9 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -665,6 +697,9 @@
       <c r="E9" s="4" t="b">
         <v>1</v>
       </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -688,6 +723,9 @@
       <c r="E10" t="b">
         <v>1</v>
       </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -711,6 +749,9 @@
       <c r="E11" s="4" t="b">
         <v>1</v>
       </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -733,6 +774,9 @@
       </c>
       <c r="E12" t="b">
         <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigExporter/xlsx/ui_page.xlsx
+++ b/ConfigExporter/xlsx/ui_page.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.625" customWidth="1" style="1" min="1" max="1"/>
@@ -779,6 +779,58 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OgsFriendListPopup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OGS 好友列表弹窗</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RecentReplayListPopup</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>最近对局列表弹窗</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ConfigExporter/xlsx/ui_page.xlsx
+++ b/ConfigExporter/xlsx/ui_page.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.625" customWidth="1" style="1" min="1" max="1"/>
@@ -831,6 +831,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OgsFriendProfilePopup</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ConfigExporter/xlsx/ui_page.xlsx
+++ b/ConfigExporter/xlsx/ui_page.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.625" customWidth="1" style="1" min="1" max="1"/>
@@ -756,24 +756,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ConfirmPopup</t>
+          <t>DuelMoveConfirmPopup</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>generic confirm popup</t>
+          <t>Duel move confirm popup</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TopMost</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -782,24 +782,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OgsFriendListPopup</t>
+          <t>ConfirmPopup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OGS 好友列表弹窗</t>
+          <t>generic confirm popup</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>TopMost</t>
         </is>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -808,12 +808,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RecentReplayListPopup</t>
+          <t>OgsFriendListPopup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>最近对局列表弹窗</t>
+          <t>OGS 好友列表弹窗</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -834,22 +834,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>RecentReplayListPopup</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>最近对局列表弹窗</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>OgsFriendProfilePopup</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="b">
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
         <v>1</v>
       </c>
     </row>
